--- a/Relay2026_Data.xlsx
+++ b/Relay2026_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chiaramanton/Library/Mobile Documents/com~apple~CloudDocs/RAGNAR RELAY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE09E7DF-7E20-6D42-BDAD-269EF97F2C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84EB8B3B-DA46-1B4C-8D5E-F7E6C86DDF01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20080" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runners" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="301">
   <si>
     <t>#</t>
   </si>
@@ -929,6 +929,21 @@
   </si>
   <si>
     <t>Parent</t>
+  </si>
+  <si>
+    <t>details</t>
+  </si>
+  <si>
+    <t>Apple Casch</t>
+  </si>
+  <si>
+    <t>Venmo</t>
+  </si>
+  <si>
+    <t>CARD</t>
+  </si>
+  <si>
+    <t>ZELLE</t>
   </si>
 </sst>
 </file>
@@ -1012,11 +1027,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1205,7 +1220,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1214,9 +1229,10 @@
     <col min="4" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="29.25" customHeight="1">
+    <row r="1" spans="1:10" ht="29.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1241,8 +1257,11 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="15">
+      <c r="J1" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1267,8 +1286,11 @@
       <c r="H2" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="15">
+      <c r="J2" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1293,8 +1315,11 @@
       <c r="H3" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="15">
+      <c r="J3" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1319,8 +1344,11 @@
       <c r="H4" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="15">
+      <c r="J4" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1345,8 +1373,9 @@
       <c r="H5" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="15">
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="15">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1365,12 +1394,13 @@
       <c r="F6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="7"/>
+      <c r="G6" s="5"/>
       <c r="H6" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="15">
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" ht="15">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1395,8 +1425,11 @@
       <c r="H7" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="15">
+      <c r="J7" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1421,8 +1454,11 @@
       <c r="H8" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="15">
+      <c r="J8" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1447,8 +1483,9 @@
       <c r="H9" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="15">
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" ht="15">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1473,8 +1510,11 @@
       <c r="H10" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="15">
+      <c r="J10" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1499,8 +1539,9 @@
       <c r="H11" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="15">
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" spans="1:10" ht="15">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1525,8 +1566,11 @@
       <c r="H12" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="15">
+      <c r="J12" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1551,8 +1595,9 @@
       <c r="H13" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="15">
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" spans="1:10" ht="15">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1577,8 +1622,11 @@
       <c r="H14" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" ht="15">
+      <c r="J14" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1603,8 +1651,11 @@
       <c r="H15" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" ht="15">
+      <c r="J15" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1623,10 +1674,11 @@
       <c r="F16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-    </row>
-    <row r="17" spans="1:8" ht="15">
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="1:10" ht="15">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1634,7 +1686,7 @@
         <v>71</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D17" s="3">
         <v>175.9</v>
@@ -1645,9 +1697,12 @@
       <c r="F17" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G17" s="7"/>
+      <c r="G17" s="5"/>
       <c r="H17" s="2" t="s">
         <v>73</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -2133,9 +2188,9 @@
       <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:5" ht="15">
       <c r="A10" s="2">
@@ -2193,9 +2248,9 @@
       <c r="B13" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:5" ht="15">
       <c r="A14" s="2">
@@ -2238,9 +2293,9 @@
       <c r="B16" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
     </row>
     <row r="17" spans="1:7" ht="15">
       <c r="A17" s="2">
@@ -4492,13 +4547,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
     </row>
     <row r="3" spans="1:5" ht="16">
       <c r="A3" s="4" t="s">

--- a/Relay2026_Data.xlsx
+++ b/Relay2026_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chiaramanton/Library/Mobile Documents/com~apple~CloudDocs/RAGNAR RELAY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84EB8B3B-DA46-1B4C-8D5E-F7E6C86DDF01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE09E7DF-7E20-6D42-BDAD-269EF97F2C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20080" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runners" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="296">
   <si>
     <t>#</t>
   </si>
@@ -929,21 +929,6 @@
   </si>
   <si>
     <t>Parent</t>
-  </si>
-  <si>
-    <t>details</t>
-  </si>
-  <si>
-    <t>Apple Casch</t>
-  </si>
-  <si>
-    <t>Venmo</t>
-  </si>
-  <si>
-    <t>CARD</t>
-  </si>
-  <si>
-    <t>ZELLE</t>
   </si>
 </sst>
 </file>
@@ -1027,11 +1012,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1220,7 +1205,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1229,10 +1214,9 @@
     <col min="4" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="29.25" customHeight="1">
+    <row r="1" spans="1:8" ht="29.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1257,11 +1241,8 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="15">
+    </row>
+    <row r="2" spans="1:8" ht="15">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1286,11 +1267,8 @@
       <c r="H2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15">
+    </row>
+    <row r="3" spans="1:8" ht="15">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1315,11 +1293,8 @@
       <c r="H3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="15">
+    </row>
+    <row r="4" spans="1:8" ht="15">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1344,11 +1319,8 @@
       <c r="H4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="15">
+    </row>
+    <row r="5" spans="1:8" ht="15">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1373,9 +1345,8 @@
       <c r="H5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="2"/>
-    </row>
-    <row r="6" spans="1:10" ht="15">
+    </row>
+    <row r="6" spans="1:8" ht="15">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1394,13 +1365,12 @@
       <c r="F6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="5"/>
+      <c r="G6" s="7"/>
       <c r="H6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="2"/>
-    </row>
-    <row r="7" spans="1:10" ht="15">
+    </row>
+    <row r="7" spans="1:8" ht="15">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1425,11 +1395,8 @@
       <c r="H7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="15">
+    </row>
+    <row r="8" spans="1:8" ht="15">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1454,11 +1421,8 @@
       <c r="H8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="15">
+    </row>
+    <row r="9" spans="1:8" ht="15">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1483,9 +1447,8 @@
       <c r="H9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="J9" s="2"/>
-    </row>
-    <row r="10" spans="1:10" ht="15">
+    </row>
+    <row r="10" spans="1:8" ht="15">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1510,11 +1473,8 @@
       <c r="H10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="J10" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="15">
+    </row>
+    <row r="11" spans="1:8" ht="15">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1539,9 +1499,8 @@
       <c r="H11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="J11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" ht="15">
+    </row>
+    <row r="12" spans="1:8" ht="15">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1566,11 +1525,8 @@
       <c r="H12" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="15">
+    </row>
+    <row r="13" spans="1:8" ht="15">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1595,9 +1551,8 @@
       <c r="H13" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="J13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" ht="15">
+    </row>
+    <row r="14" spans="1:8" ht="15">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1622,11 +1577,8 @@
       <c r="H14" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="J14" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="15">
+    </row>
+    <row r="15" spans="1:8" ht="15">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1651,11 +1603,8 @@
       <c r="H15" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="J15" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="15">
+    </row>
+    <row r="16" spans="1:8" ht="15">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1674,11 +1623,10 @@
       <c r="F16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="J16" s="2"/>
-    </row>
-    <row r="17" spans="1:10" ht="15">
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+    </row>
+    <row r="17" spans="1:8" ht="15">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1686,7 +1634,7 @@
         <v>71</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D17" s="3">
         <v>175.9</v>
@@ -1697,12 +1645,9 @@
       <c r="F17" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G17" s="5"/>
+      <c r="G17" s="7"/>
       <c r="H17" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -2188,9 +2133,9 @@
       <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
     </row>
     <row r="10" spans="1:5" ht="15">
       <c r="A10" s="2">
@@ -2248,9 +2193,9 @@
       <c r="B13" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
     </row>
     <row r="14" spans="1:5" ht="15">
       <c r="A14" s="2">
@@ -2293,9 +2238,9 @@
       <c r="B16" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
     </row>
     <row r="17" spans="1:7" ht="15">
       <c r="A17" s="2">
@@ -4547,13 +4492,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
     </row>
     <row r="3" spans="1:5" ht="16">
       <c r="A3" s="4" t="s">

--- a/Relay2026_Data.xlsx
+++ b/Relay2026_Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chiaramanton/Library/Mobile Documents/com~apple~CloudDocs/RAGNAR RELAY/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chiaramanton/Downloads/Relay2026_v8_about_cost_ROOT_FILES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE09E7DF-7E20-6D42-BDAD-269EF97F2C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0803FF-91C0-9F48-A266-27F4C448EF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20080" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20080" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runners" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="292">
   <si>
     <t>#</t>
   </si>
@@ -514,9 +514,6 @@
     <t>Chiara</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>Camp Table Food (need 1)</t>
   </si>
   <si>
@@ -535,9 +532,6 @@
     <t>Tarps Blue</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>Tarp Clips / Bungie Cords</t>
   </si>
   <si>
@@ -553,9 +547,6 @@
     <t>Everyone</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>Camp Lighting/Lanterns</t>
   </si>
   <si>
@@ -563,9 +554,6 @@
   </si>
   <si>
     <t>Dulce</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>Camp Lights Ground</t>
@@ -998,7 +986,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1012,9 +1000,12 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1365,7 +1356,7 @@
       <c r="F6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="7"/>
+      <c r="G6" s="5"/>
       <c r="H6" s="2" t="s">
         <v>30</v>
       </c>
@@ -1623,8 +1614,8 @@
       <c r="F16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" ht="15">
       <c r="A17" s="2">
@@ -1634,7 +1625,7 @@
         <v>71</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D17" s="3">
         <v>175.9</v>
@@ -1645,7 +1636,7 @@
       <c r="F17" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G17" s="7"/>
+      <c r="G17" s="5"/>
       <c r="H17" s="2" t="s">
         <v>73</v>
       </c>
@@ -2069,7 +2060,7 @@
         <v>96</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>97</v>
@@ -2086,7 +2077,7 @@
         <v>96</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>97</v>
@@ -2117,13 +2108,13 @@
         <v>35</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>94</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15">
@@ -2133,9 +2124,9 @@
       <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:5" ht="15">
       <c r="A10" s="2">
@@ -2193,9 +2184,9 @@
       <c r="B13" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:5" ht="15">
       <c r="A14" s="2">
@@ -2205,13 +2196,13 @@
         <v>61</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>88</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15">
@@ -2222,13 +2213,13 @@
         <v>65</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>107</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15">
@@ -2238,9 +2229,9 @@
       <c r="B16" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
     </row>
     <row r="17" spans="1:7" ht="15">
       <c r="A17" s="2">
@@ -2250,13 +2241,13 @@
         <v>71</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>99</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2688,8 +2679,8 @@
       <c r="E2" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>157</v>
+      <c r="F2" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15">
@@ -2697,7 +2688,7 @@
         <v>153</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>155</v>
@@ -2708,8 +2699,8 @@
       <c r="E3" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>157</v>
+      <c r="F3" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15">
@@ -2717,7 +2708,7 @@
         <v>153</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>115</v>
@@ -2726,10 +2717,10 @@
         <v>116</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
+      </c>
+      <c r="F4" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15">
@@ -2737,7 +2728,7 @@
         <v>153</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>115</v>
@@ -2746,10 +2737,10 @@
         <v>116</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
+      </c>
+      <c r="F5" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15">
@@ -2757,7 +2748,7 @@
         <v>153</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>115</v>
@@ -2768,8 +2759,8 @@
       <c r="E6" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>164</v>
+      <c r="F6" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15">
@@ -2777,7 +2768,7 @@
         <v>153</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>115</v>
@@ -2788,54 +2779,54 @@
       <c r="E7" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>164</v>
+      <c r="F7" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15">
       <c r="A8" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="F8" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15">
       <c r="A9" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="2" t="s">
-        <v>157</v>
+      <c r="F9" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15">
       <c r="A10" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>155</v>
@@ -2844,154 +2835,154 @@
         <v>116</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
+      </c>
+      <c r="F10" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15">
       <c r="A11" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" ht="15">
       <c r="A12" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="F12" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15">
       <c r="A13" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="F13" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15">
       <c r="A14" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="F14" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15">
       <c r="A15" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="F15" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15">
       <c r="A16" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="F16" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15">
       <c r="A17" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>157</v>
+        <v>167</v>
+      </c>
+      <c r="F17" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15">
       <c r="A18" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>115</v>
@@ -3002,16 +2993,16 @@
       <c r="E18" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>157</v>
+      <c r="F18" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15">
       <c r="A19" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>155</v>
@@ -3020,34 +3011,34 @@
         <v>116</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>157</v>
+        <v>182</v>
+      </c>
+      <c r="F19" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15">
       <c r="A20" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="2" t="s">
-        <v>157</v>
+      <c r="F20" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15">
       <c r="A21" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>155</v>
@@ -3055,171 +3046,171 @@
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15">
       <c r="A22" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15">
       <c r="A23" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15">
       <c r="A24" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="2" t="s">
-        <v>157</v>
+      <c r="F24" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15">
       <c r="A25" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="F25" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15">
       <c r="A26" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="F26" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15">
       <c r="A27" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="F27" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15">
       <c r="A28" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>197</v>
-      </c>
       <c r="C28" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="F28" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15">
       <c r="A29" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="F29" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15">
       <c r="A30" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>155</v>
@@ -3230,48 +3221,48 @@
       <c r="E30" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>157</v>
+      <c r="F30" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15">
       <c r="A31" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="2" t="s">
-        <v>157</v>
+      <c r="F31" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15">
       <c r="A32" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
-      <c r="F32" s="2" t="s">
-        <v>157</v>
+      <c r="F32" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15">
       <c r="A33" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>155</v>
@@ -3279,15 +3270,15 @@
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15">
       <c r="A34" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>155</v>
@@ -3295,15 +3286,15 @@
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15">
       <c r="A35" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>155</v>
@@ -3311,15 +3302,15 @@
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15">
       <c r="A36" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>155</v>
@@ -3327,15 +3318,15 @@
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15">
       <c r="A37" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>155</v>
@@ -3343,15 +3334,15 @@
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15">
       <c r="A38" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>155</v>
@@ -3359,15 +3350,15 @@
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15">
       <c r="A39" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>155</v>
@@ -3375,15 +3366,15 @@
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15">
       <c r="A40" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>155</v>
@@ -3391,515 +3382,515 @@
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15">
       <c r="A41" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="F41" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15">
       <c r="A42" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15">
       <c r="A43" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15">
       <c r="A44" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>214</v>
-      </c>
       <c r="C44" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15">
       <c r="A45" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="F45" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15">
       <c r="A46" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15">
       <c r="A47" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="F47" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15">
       <c r="A48" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="F48" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15">
       <c r="A49" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="F49" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15">
       <c r="A50" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15">
       <c r="A51" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="F51" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15">
       <c r="A52" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="F52" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15">
       <c r="A53" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="F53" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15">
       <c r="A54" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15">
       <c r="A55" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15">
       <c r="A56" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15">
       <c r="A57" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15">
       <c r="A58" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="F58" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15">
       <c r="A59" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="F59" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15">
       <c r="A60" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>231</v>
-      </c>
       <c r="C60" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="F60" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15">
       <c r="A61" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15">
       <c r="A62" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15">
       <c r="A63" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15">
       <c r="A64" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="15">
       <c r="A65" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="15">
       <c r="A66" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>155</v>
@@ -3908,318 +3899,318 @@
         <v>116</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>157</v>
+        <v>235</v>
+      </c>
+      <c r="F66" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="15">
       <c r="A67" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>170</v>
+      <c r="F67" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="15">
       <c r="A68" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="F68" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="15">
       <c r="A69" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="F69" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="15">
       <c r="A70" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="F70" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15">
       <c r="A71" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="F71" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="15">
       <c r="A72" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15">
       <c r="A73" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="15">
       <c r="A74" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="15">
       <c r="A75" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="15">
       <c r="A76" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="15">
       <c r="A77" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="15">
       <c r="A78" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="15">
       <c r="A79" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="15">
       <c r="A80" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="15">
       <c r="A81" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="15">
       <c r="A82" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>115</v>
@@ -4228,18 +4219,18 @@
         <v>116</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>157</v>
+        <v>182</v>
+      </c>
+      <c r="F82" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="15">
       <c r="A83" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>115</v>
@@ -4248,18 +4239,18 @@
         <v>116</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
+      </c>
+      <c r="F83" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="15">
       <c r="A84" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>155</v>
@@ -4267,47 +4258,47 @@
       <c r="D84" s="2"/>
       <c r="E84" s="2"/>
       <c r="F84" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="15">
       <c r="A85" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
-      <c r="F85" s="2" t="s">
-        <v>174</v>
+      <c r="F85" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="15">
       <c r="A86" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B86" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>260</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
-      <c r="F86" s="2" t="s">
-        <v>174</v>
+      <c r="F86" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="15">
       <c r="A87" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>155</v>
@@ -4316,128 +4307,128 @@
         <v>116</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>157</v>
+        <v>170</v>
+      </c>
+      <c r="F87" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="15">
       <c r="A88" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>170</v>
+        <v>260</v>
+      </c>
+      <c r="F88" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="15">
       <c r="A89" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="15">
       <c r="A90" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
-      <c r="F90" s="2" t="s">
-        <v>157</v>
+      <c r="F90" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="15">
       <c r="A91" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
-      <c r="F91" s="2" t="s">
-        <v>157</v>
+      <c r="F91" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="15">
       <c r="A92" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
-      <c r="F92" s="2" t="s">
-        <v>157</v>
+      <c r="F92" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="15">
       <c r="A93" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
-      <c r="F93" s="2" t="s">
-        <v>157</v>
+      <c r="F93" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="15">
       <c r="A94" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" s="2"/>
-      <c r="F94" s="2" t="s">
-        <v>157</v>
+      <c r="F94" s="8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4459,23 +4450,23 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15">
       <c r="A2" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15">
       <c r="A3" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -4488,66 +4479,67 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="2" width="40" customWidth="1"/>
+    <col min="1" max="1" width="85.83203125" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21">
-      <c r="A1" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
+      <c r="A1" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
     </row>
     <row r="3" spans="1:5" ht="16">
       <c r="A3" s="4" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:5" ht="15">
       <c r="A4" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:5" ht="15">
       <c r="A5" s="2" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B5" s="2"/>
     </row>
     <row r="6" spans="1:5" ht="15">
       <c r="A6" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B6" s="2"/>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5" ht="15">
       <c r="A7" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B7" s="2"/>
     </row>
-    <row r="8" spans="1:5" ht="30">
+    <row r="8" spans="1:5" ht="15">
       <c r="A8" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="15">
       <c r="A9" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B9" s="2"/>
     </row>
     <row r="10" spans="1:5" ht="15">
       <c r="A10" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>

--- a/Relay2026_Data.xlsx
+++ b/Relay2026_Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chiaramanton/Downloads/Relay2026_v8_about_cost_ROOT_FILES/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chiaramanton/Library/Mobile Documents/com~apple~CloudDocs/RAGNAR RELAY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0803FF-91C0-9F48-A266-27F4C448EF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F23C0899-0AC6-C94C-99DE-27BAD70990DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20080" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runners" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="306">
   <si>
     <t>#</t>
   </si>
@@ -514,6 +514,9 @@
     <t>Chiara</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>Camp Table Food (need 1)</t>
   </si>
   <si>
@@ -532,6 +535,9 @@
     <t>Tarps Blue</t>
   </si>
   <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>Tarp Clips / Bungie Cords</t>
   </si>
   <si>
@@ -547,6 +553,9 @@
     <t>Everyone</t>
   </si>
   <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>Camp Lighting/Lanterns</t>
   </si>
   <si>
@@ -556,6 +565,9 @@
     <t>Dulce</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>Camp Lights Ground</t>
   </si>
   <si>
@@ -917,6 +929,36 @@
   </si>
   <si>
     <t>Parent</t>
+  </si>
+  <si>
+    <t>details</t>
+  </si>
+  <si>
+    <t>CARD</t>
+  </si>
+  <si>
+    <t>ZELLE</t>
+  </si>
+  <si>
+    <t>Apple Cash</t>
+  </si>
+  <si>
+    <t>VENMO 07/03</t>
+  </si>
+  <si>
+    <t>VENMO 06/30</t>
+  </si>
+  <si>
+    <t>ZELLE 07/03</t>
+  </si>
+  <si>
+    <t>ZELLE 06/29</t>
+  </si>
+  <si>
+    <t>ZELLE 06/28</t>
+  </si>
+  <si>
+    <t>612-501-0468</t>
   </si>
 </sst>
 </file>
@@ -1005,7 +1047,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1196,7 +1238,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1205,9 +1247,10 @@
     <col min="4" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="10" max="10" width="22.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="29.25" customHeight="1">
+    <row r="1" spans="1:10" ht="29.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1232,8 +1275,11 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="15">
+      <c r="J1" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1258,8 +1304,11 @@
       <c r="H2" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="15">
+      <c r="J2" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1284,8 +1333,11 @@
       <c r="H3" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="15">
+      <c r="J3" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1310,8 +1362,11 @@
       <c r="H4" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="15">
+      <c r="J4" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1336,8 +1391,9 @@
       <c r="H5" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="15">
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="15">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1360,8 +1416,9 @@
       <c r="H6" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="15">
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" ht="15">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1386,8 +1443,11 @@
       <c r="H7" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="15">
+      <c r="J7" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1412,8 +1472,11 @@
       <c r="H8" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="15">
+      <c r="J8" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1421,7 +1484,7 @@
         <v>40</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D9" s="3">
         <v>175.9</v>
@@ -1438,8 +1501,11 @@
       <c r="H9" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="15">
+      <c r="J9" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1464,8 +1530,11 @@
       <c r="H10" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="15">
+      <c r="J10" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1473,7 +1542,7 @@
         <v>49</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D11" s="3">
         <v>175.9</v>
@@ -1490,8 +1559,11 @@
       <c r="H11" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="15">
+      <c r="J11" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1516,8 +1588,11 @@
       <c r="H12" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="15">
+      <c r="J12" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1542,8 +1617,9 @@
       <c r="H13" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="15">
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" spans="1:10" ht="15">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1568,8 +1644,11 @@
       <c r="H14" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" ht="15">
+      <c r="J14" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1594,8 +1673,11 @@
       <c r="H15" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" ht="15">
+      <c r="J15" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1603,7 +1685,7 @@
         <v>69</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D16" s="3">
         <v>175.9</v>
@@ -1615,9 +1697,14 @@
         <v>11</v>
       </c>
       <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-    </row>
-    <row r="17" spans="1:8" ht="15">
+      <c r="H16" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1639,6 +1726,9 @@
       <c r="G17" s="5"/>
       <c r="H17" s="2" t="s">
         <v>73</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -2060,7 +2150,7 @@
         <v>96</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>97</v>
@@ -2077,7 +2167,7 @@
         <v>96</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>97</v>
@@ -2108,13 +2198,13 @@
         <v>35</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>94</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15">
@@ -2196,13 +2286,13 @@
         <v>61</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>88</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15">
@@ -2213,13 +2303,13 @@
         <v>65</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>107</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15">
@@ -2241,13 +2331,13 @@
         <v>71</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>99</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2679,8 +2769,8 @@
       <c r="E2" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="F2" s="8">
-        <v>1</v>
+      <c r="F2" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15">
@@ -2688,7 +2778,7 @@
         <v>153</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>155</v>
@@ -2699,8 +2789,8 @@
       <c r="E3" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F3" s="8">
-        <v>1</v>
+      <c r="F3" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15">
@@ -2708,7 +2798,7 @@
         <v>153</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>115</v>
@@ -2717,10 +2807,10 @@
         <v>116</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F4" s="8">
-        <v>1</v>
+        <v>160</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15">
@@ -2728,7 +2818,7 @@
         <v>153</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>115</v>
@@ -2737,10 +2827,10 @@
         <v>116</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F5" s="8">
-        <v>1</v>
+        <v>162</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15">
@@ -2748,7 +2838,7 @@
         <v>153</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>115</v>
@@ -2759,8 +2849,8 @@
       <c r="E6" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F6" s="8">
-        <v>6</v>
+      <c r="F6" s="2" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15">
@@ -2768,7 +2858,7 @@
         <v>153</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>115</v>
@@ -2779,54 +2869,54 @@
       <c r="E7" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F7" s="8">
-        <v>6</v>
+      <c r="F7" s="2" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15">
       <c r="A8" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F8" s="8">
-        <v>16</v>
+        <v>169</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15">
       <c r="A9" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="8">
-        <v>1</v>
+      <c r="F9" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15">
       <c r="A10" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>155</v>
@@ -2835,154 +2925,154 @@
         <v>116</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="F10" s="8">
-        <v>2</v>
+        <v>173</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15">
       <c r="A11" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" ht="15">
       <c r="A12" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F12" s="8">
-        <v>16</v>
+        <v>169</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15">
       <c r="A13" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F13" s="8">
-        <v>16</v>
+        <v>169</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15">
       <c r="A14" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F14" s="8">
-        <v>16</v>
+        <v>169</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15">
       <c r="A15" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F15" s="8">
-        <v>16</v>
+        <v>169</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15">
       <c r="A16" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F16" s="8">
-        <v>16</v>
+        <v>169</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15">
       <c r="A17" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F17" s="8">
-        <v>1</v>
+        <v>169</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15">
       <c r="A18" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>115</v>
@@ -2993,16 +3083,16 @@
       <c r="E18" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="F18" s="8">
-        <v>1</v>
+      <c r="F18" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15">
       <c r="A19" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>155</v>
@@ -3011,34 +3101,34 @@
         <v>116</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="F19" s="8">
-        <v>1</v>
+        <v>186</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15">
       <c r="A20" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="8">
-        <v>1</v>
+      <c r="F20" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15">
       <c r="A21" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>155</v>
@@ -3046,171 +3136,171 @@
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15">
       <c r="A22" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15">
       <c r="A23" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15">
       <c r="A24" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="8">
-        <v>1</v>
+      <c r="F24" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15">
       <c r="A25" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F25" s="8">
-        <v>16</v>
+        <v>169</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15">
       <c r="A26" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F26" s="8">
-        <v>16</v>
+        <v>169</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15">
       <c r="A27" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F27" s="8">
-        <v>16</v>
+        <v>169</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15">
       <c r="A28" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F28" s="8">
-        <v>16</v>
+        <v>169</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15">
       <c r="A29" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F29" s="8">
-        <v>16</v>
+        <v>169</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15">
       <c r="A30" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>155</v>
@@ -3221,48 +3311,48 @@
       <c r="E30" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="F30" s="8">
-        <v>1</v>
+      <c r="F30" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15">
       <c r="A31" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="8">
-        <v>1</v>
+      <c r="F31" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15">
       <c r="A32" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
-      <c r="F32" s="8">
-        <v>1</v>
+      <c r="F32" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15">
       <c r="A33" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>155</v>
@@ -3270,15 +3360,15 @@
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15">
       <c r="A34" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>155</v>
@@ -3286,15 +3376,15 @@
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15">
       <c r="A35" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>155</v>
@@ -3302,15 +3392,15 @@
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15">
       <c r="A36" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>155</v>
@@ -3318,15 +3408,15 @@
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15">
       <c r="A37" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>155</v>
@@ -3334,15 +3424,15 @@
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15">
       <c r="A38" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>155</v>
@@ -3350,15 +3440,15 @@
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15">
       <c r="A39" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>155</v>
@@ -3366,15 +3456,15 @@
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15">
       <c r="A40" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>155</v>
@@ -3382,515 +3472,515 @@
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15">
       <c r="A41" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F41" s="8">
-        <v>16</v>
+        <v>169</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15">
       <c r="A42" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15">
       <c r="A43" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15">
       <c r="A44" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15">
       <c r="A45" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F45" s="8">
-        <v>16</v>
+        <v>169</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15">
       <c r="A46" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15">
       <c r="A47" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F47" s="8">
-        <v>16</v>
+        <v>169</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15">
       <c r="A48" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F48" s="8">
-        <v>16</v>
+        <v>169</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15">
       <c r="A49" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F49" s="8">
-        <v>16</v>
+        <v>169</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15">
       <c r="A50" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15">
       <c r="A51" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F51" s="8">
-        <v>16</v>
+        <v>169</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15">
       <c r="A52" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F52" s="8">
-        <v>16</v>
+        <v>169</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15">
       <c r="A53" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F53" s="8">
-        <v>16</v>
+        <v>169</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15">
       <c r="A54" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15">
       <c r="A55" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15">
       <c r="A56" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15">
       <c r="A57" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15">
       <c r="A58" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F58" s="8">
-        <v>16</v>
+        <v>169</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15">
       <c r="A59" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F59" s="8">
-        <v>16</v>
+        <v>169</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15">
       <c r="A60" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F60" s="8">
-        <v>16</v>
+        <v>169</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15">
       <c r="A61" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15">
       <c r="A62" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15">
       <c r="A63" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15">
       <c r="A64" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="15">
       <c r="A65" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="15">
       <c r="A66" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>155</v>
@@ -3899,318 +3989,318 @@
         <v>116</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F66" s="8">
-        <v>1</v>
+        <v>239</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="15">
       <c r="A67" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="F67" s="8">
-        <v>16</v>
+        <v>241</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="15">
       <c r="A68" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F68" s="8">
-        <v>16</v>
+        <v>169</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="15">
       <c r="A69" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F69" s="8">
-        <v>16</v>
+        <v>169</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="15">
       <c r="A70" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F70" s="8">
-        <v>16</v>
+        <v>169</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15">
       <c r="A71" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F71" s="8">
-        <v>16</v>
+        <v>169</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="15">
       <c r="A72" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15">
       <c r="A73" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="15">
       <c r="A74" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="15">
       <c r="A75" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="15">
       <c r="A76" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="15">
       <c r="A77" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="15">
       <c r="A78" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="15">
       <c r="A79" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="15">
       <c r="A80" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="15">
       <c r="A81" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="15">
       <c r="A82" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>115</v>
@@ -4219,18 +4309,18 @@
         <v>116</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="F82" s="8">
-        <v>1</v>
+        <v>186</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="15">
       <c r="A83" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>115</v>
@@ -4239,18 +4329,18 @@
         <v>116</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F83" s="8">
-        <v>1</v>
+        <v>162</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="15">
       <c r="A84" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>155</v>
@@ -4258,47 +4348,47 @@
       <c r="D84" s="2"/>
       <c r="E84" s="2"/>
       <c r="F84" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="15">
       <c r="A85" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
-      <c r="F85" s="8">
-        <v>2</v>
+      <c r="F85" s="2" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="15">
       <c r="A86" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
-      <c r="F86" s="8">
-        <v>2</v>
+      <c r="F86" s="2" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="15">
       <c r="A87" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>155</v>
@@ -4307,128 +4397,128 @@
         <v>116</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="F87" s="8">
-        <v>1</v>
+        <v>173</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="15">
       <c r="A88" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="F88" s="8">
-        <v>16</v>
+        <v>264</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="15">
       <c r="A89" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="15">
       <c r="A90" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
-      <c r="F90" s="8">
-        <v>1</v>
+      <c r="F90" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="15">
       <c r="A91" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
-      <c r="F91" s="8">
-        <v>1</v>
+      <c r="F91" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="15">
       <c r="A92" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
-      <c r="F92" s="8">
-        <v>1</v>
+      <c r="F92" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="15">
       <c r="A93" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
-      <c r="F93" s="8">
-        <v>1</v>
+      <c r="F93" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="15">
       <c r="A94" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" s="2"/>
-      <c r="F94" s="8">
-        <v>1</v>
+      <c r="F94" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -4450,23 +4540,23 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15">
       <c r="A2" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15">
       <c r="A3" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -4479,13 +4569,12 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="85.83203125" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="1" max="2" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21">
       <c r="A1" s="6" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -4494,52 +4583,52 @@
     </row>
     <row r="3" spans="1:5" ht="16">
       <c r="A3" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:5" ht="15">
       <c r="A4" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:5" ht="15">
       <c r="A5" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B5" s="2"/>
     </row>
     <row r="6" spans="1:5" ht="15">
       <c r="A6" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B6" s="2"/>
     </row>
-    <row r="7" spans="1:5" ht="15">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B7" s="2"/>
     </row>
-    <row r="8" spans="1:5" ht="15">
+    <row r="8" spans="1:5" ht="30">
       <c r="A8" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:5" ht="15">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B9" s="2"/>
     </row>
     <row r="10" spans="1:5" ht="15">
       <c r="A10" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>

--- a/Relay2026_Data.xlsx
+++ b/Relay2026_Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chiaramanton/Library/Mobile Documents/com~apple~CloudDocs/RAGNAR RELAY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F23C0899-0AC6-C94C-99DE-27BAD70990DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64C4759-7F66-E140-8D78-8CC8B1A30D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="314">
   <si>
     <t>#</t>
   </si>
@@ -937,9 +937,6 @@
     <t>CARD</t>
   </si>
   <si>
-    <t>ZELLE</t>
-  </si>
-  <si>
     <t>Apple Cash</t>
   </si>
   <si>
@@ -959,6 +956,33 @@
   </si>
   <si>
     <t>612-501-0468</t>
+  </si>
+  <si>
+    <t>ZELLE 07/31 $185.71</t>
+  </si>
+  <si>
+    <t>VENMO 07/07</t>
+  </si>
+  <si>
+    <t>emily.umulis@gmail.com</t>
+  </si>
+  <si>
+    <t>David Umulis</t>
+  </si>
+  <si>
+    <t>Mike Huguenel</t>
+  </si>
+  <si>
+    <t>305-497-5684</t>
+  </si>
+  <si>
+    <t>Eduardo Pelaez</t>
+  </si>
+  <si>
+    <t>786-510-0370</t>
+  </si>
+  <si>
+    <t>Brother</t>
   </si>
 </sst>
 </file>
@@ -1363,7 +1387,7 @@
         <v>23</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15">
@@ -1374,7 +1398,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3">
         <v>175.9</v>
@@ -1391,7 +1415,9 @@
       <c r="H5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="2"/>
+      <c r="J5" s="2" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="15">
       <c r="A6" s="2">
@@ -1401,7 +1427,7 @@
         <v>28</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D6" s="3">
         <v>175.9</v>
@@ -1416,7 +1442,9 @@
       <c r="H6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="2"/>
+      <c r="J6" s="2" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row r="7" spans="1:10" ht="15">
       <c r="A7" s="2">
@@ -1444,7 +1472,7 @@
         <v>34</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15">
@@ -1473,7 +1501,7 @@
         <v>39</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15">
@@ -1502,7 +1530,7 @@
         <v>43</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15">
@@ -1531,7 +1559,7 @@
         <v>48</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15">
@@ -1560,7 +1588,7 @@
         <v>52</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15">
@@ -1589,7 +1617,7 @@
         <v>56</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15">
@@ -1600,7 +1628,7 @@
         <v>57</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D13" s="3">
         <v>175.9</v>
@@ -1617,7 +1645,9 @@
       <c r="H13" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="J13" s="2"/>
+      <c r="J13" s="2" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="14" spans="1:10" ht="15">
       <c r="A14" s="2">
@@ -1645,7 +1675,7 @@
         <v>64</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15">
@@ -1674,7 +1704,7 @@
         <v>68</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15">
@@ -1696,12 +1726,14 @@
       <c r="F16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="8" t="s">
-        <v>305</v>
+      <c r="G16" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>304</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15">
@@ -1728,7 +1760,7 @@
         <v>73</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -2214,9 +2246,15 @@
       <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
+      <c r="C9" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="15">
       <c r="A10" s="2">
@@ -2245,7 +2283,9 @@
       <c r="C11" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" s="2" t="s">
+        <v>107</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>105</v>
       </c>
@@ -2274,9 +2314,15 @@
       <c r="B13" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
+      <c r="C13" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="14" spans="1:5" ht="15">
       <c r="A14" s="2">
@@ -2319,9 +2365,15 @@
       <c r="B16" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
+      <c r="C16" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="17" spans="1:7" ht="15">
       <c r="A17" s="2">
@@ -4569,7 +4621,8 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="2" width="40" customWidth="1"/>
+    <col min="1" max="1" width="81.83203125" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21">
@@ -4605,19 +4658,19 @@
       </c>
       <c r="B6" s="2"/>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5" ht="15">
       <c r="A7" s="2" t="s">
         <v>282</v>
       </c>
       <c r="B7" s="2"/>
     </row>
-    <row r="8" spans="1:5" ht="30">
+    <row r="8" spans="1:5" ht="15">
       <c r="A8" s="2" t="s">
         <v>283</v>
       </c>
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="15">
       <c r="A9" s="2" t="s">
         <v>284</v>
       </c>

--- a/Relay2026_Data.xlsx
+++ b/Relay2026_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chiaramanton/Library/Mobile Documents/com~apple~CloudDocs/RAGNAR RELAY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64C4759-7F66-E140-8D78-8CC8B1A30D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE09E7DF-7E20-6D42-BDAD-269EF97F2C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20080" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runners" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="296">
   <si>
     <t>#</t>
   </si>
@@ -929,60 +929,6 @@
   </si>
   <si>
     <t>Parent</t>
-  </si>
-  <si>
-    <t>details</t>
-  </si>
-  <si>
-    <t>CARD</t>
-  </si>
-  <si>
-    <t>Apple Cash</t>
-  </si>
-  <si>
-    <t>VENMO 07/03</t>
-  </si>
-  <si>
-    <t>VENMO 06/30</t>
-  </si>
-  <si>
-    <t>ZELLE 07/03</t>
-  </si>
-  <si>
-    <t>ZELLE 06/29</t>
-  </si>
-  <si>
-    <t>ZELLE 06/28</t>
-  </si>
-  <si>
-    <t>612-501-0468</t>
-  </si>
-  <si>
-    <t>ZELLE 07/31 $185.71</t>
-  </si>
-  <si>
-    <t>VENMO 07/07</t>
-  </si>
-  <si>
-    <t>emily.umulis@gmail.com</t>
-  </si>
-  <si>
-    <t>David Umulis</t>
-  </si>
-  <si>
-    <t>Mike Huguenel</t>
-  </si>
-  <si>
-    <t>305-497-5684</t>
-  </si>
-  <si>
-    <t>Eduardo Pelaez</t>
-  </si>
-  <si>
-    <t>786-510-0370</t>
-  </si>
-  <si>
-    <t>Brother</t>
   </si>
 </sst>
 </file>
@@ -1052,7 +998,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1066,12 +1012,9 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1262,7 +1205,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1271,10 +1214,9 @@
     <col min="4" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="10" max="10" width="22.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="29.25" customHeight="1">
+    <row r="1" spans="1:8" ht="29.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1299,11 +1241,8 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="15">
+    </row>
+    <row r="2" spans="1:8" ht="15">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1328,11 +1267,8 @@
       <c r="H2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15">
+    </row>
+    <row r="3" spans="1:8" ht="15">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1357,11 +1293,8 @@
       <c r="H3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="15">
+    </row>
+    <row r="4" spans="1:8" ht="15">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1386,11 +1319,8 @@
       <c r="H4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="15">
+    </row>
+    <row r="5" spans="1:8" ht="15">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1398,7 +1328,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D5" s="3">
         <v>175.9</v>
@@ -1415,11 +1345,8 @@
       <c r="H5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="15">
+    </row>
+    <row r="6" spans="1:8" ht="15">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1427,7 +1354,7 @@
         <v>28</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D6" s="3">
         <v>175.9</v>
@@ -1438,15 +1365,12 @@
       <c r="F6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="5"/>
+      <c r="G6" s="7"/>
       <c r="H6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="15">
+    </row>
+    <row r="7" spans="1:8" ht="15">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1471,11 +1395,8 @@
       <c r="H7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="15">
+    </row>
+    <row r="8" spans="1:8" ht="15">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1500,11 +1421,8 @@
       <c r="H8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="15">
+    </row>
+    <row r="9" spans="1:8" ht="15">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1512,7 +1430,7 @@
         <v>40</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D9" s="3">
         <v>175.9</v>
@@ -1529,11 +1447,8 @@
       <c r="H9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="15">
+    </row>
+    <row r="10" spans="1:8" ht="15">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1558,11 +1473,8 @@
       <c r="H10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="J10" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="15">
+    </row>
+    <row r="11" spans="1:8" ht="15">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1570,7 +1482,7 @@
         <v>49</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D11" s="3">
         <v>175.9</v>
@@ -1587,11 +1499,8 @@
       <c r="H11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="15">
+    </row>
+    <row r="12" spans="1:8" ht="15">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1616,11 +1525,8 @@
       <c r="H12" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="15">
+    </row>
+    <row r="13" spans="1:8" ht="15">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1628,7 +1534,7 @@
         <v>57</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D13" s="3">
         <v>175.9</v>
@@ -1645,11 +1551,8 @@
       <c r="H13" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="J13" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="15">
+    </row>
+    <row r="14" spans="1:8" ht="15">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1674,11 +1577,8 @@
       <c r="H14" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="J14" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="15">
+    </row>
+    <row r="15" spans="1:8" ht="15">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1703,11 +1603,8 @@
       <c r="H15" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="J15" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="15">
+    </row>
+    <row r="16" spans="1:8" ht="15">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1715,7 +1612,7 @@
         <v>69</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D16" s="3">
         <v>175.9</v>
@@ -1726,17 +1623,10 @@
       <c r="F16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="15">
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+    </row>
+    <row r="17" spans="1:8" ht="15">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1744,7 +1634,7 @@
         <v>71</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D17" s="3">
         <v>175.9</v>
@@ -1755,12 +1645,9 @@
       <c r="F17" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G17" s="5"/>
+      <c r="G17" s="7"/>
       <c r="H17" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -2246,15 +2133,9 @@
       <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>310</v>
-      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
     </row>
     <row r="10" spans="1:5" ht="15">
       <c r="A10" s="2">
@@ -2283,9 +2164,7 @@
       <c r="C11" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>107</v>
-      </c>
+      <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
         <v>105</v>
       </c>
@@ -2314,15 +2193,9 @@
       <c r="B13" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>312</v>
-      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
     </row>
     <row r="14" spans="1:5" ht="15">
       <c r="A14" s="2">
@@ -2365,15 +2238,9 @@
       <c r="B16" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>304</v>
-      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
     </row>
     <row r="17" spans="1:7" ht="15">
       <c r="A17" s="2">
@@ -4621,18 +4488,17 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="81.83203125" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="1" max="2" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
     </row>
     <row r="3" spans="1:5" ht="16">
       <c r="A3" s="4" t="s">
@@ -4658,19 +4524,19 @@
       </c>
       <c r="B6" s="2"/>
     </row>
-    <row r="7" spans="1:5" ht="15">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="2" t="s">
         <v>282</v>
       </c>
       <c r="B7" s="2"/>
     </row>
-    <row r="8" spans="1:5" ht="15">
+    <row r="8" spans="1:5" ht="30">
       <c r="A8" s="2" t="s">
         <v>283</v>
       </c>
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:5" ht="15">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9" s="2" t="s">
         <v>284</v>
       </c>

--- a/Relay2026_Data.xlsx
+++ b/Relay2026_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chiaramanton/Library/Mobile Documents/com~apple~CloudDocs/RAGNAR RELAY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE09E7DF-7E20-6D42-BDAD-269EF97F2C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0569EEF3-1072-9248-9E3D-70B15FA830CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20080" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12480" yWindow="660" windowWidth="22080" windowHeight="20060" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runners" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="304">
   <si>
     <t>#</t>
   </si>
@@ -929,6 +929,30 @@
   </si>
   <si>
     <t>Parent</t>
+  </si>
+  <si>
+    <t>emily.umulis@gmail.com</t>
+  </si>
+  <si>
+    <t>612-501-0468</t>
+  </si>
+  <si>
+    <t>Mike Huguenel</t>
+  </si>
+  <si>
+    <t>305-497-5684</t>
+  </si>
+  <si>
+    <t>Eduardo Pelaez</t>
+  </si>
+  <si>
+    <t>Brother</t>
+  </si>
+  <si>
+    <t>786-510-0370</t>
+  </si>
+  <si>
+    <t>David Umulis</t>
   </si>
 </sst>
 </file>
@@ -998,7 +1022,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1012,9 +1036,12 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1328,7 +1355,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3">
         <v>175.9</v>
@@ -1354,7 +1381,7 @@
         <v>28</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D6" s="3">
         <v>175.9</v>
@@ -1365,7 +1392,7 @@
       <c r="F6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="7"/>
+      <c r="G6" s="5"/>
       <c r="H6" s="2" t="s">
         <v>30</v>
       </c>
@@ -1430,7 +1457,7 @@
         <v>40</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D9" s="3">
         <v>175.9</v>
@@ -1482,7 +1509,7 @@
         <v>49</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D11" s="3">
         <v>175.9</v>
@@ -1534,7 +1561,7 @@
         <v>57</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D13" s="3">
         <v>175.9</v>
@@ -1612,7 +1639,7 @@
         <v>69</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D16" s="3">
         <v>175.9</v>
@@ -1623,8 +1650,12 @@
       <c r="F16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
+      <c r="G16" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="17" spans="1:8" ht="15">
       <c r="A17" s="2">
@@ -1634,7 +1665,7 @@
         <v>71</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D17" s="3">
         <v>175.9</v>
@@ -1645,7 +1676,7 @@
       <c r="F17" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G17" s="7"/>
+      <c r="G17" s="5"/>
       <c r="H17" s="2" t="s">
         <v>73</v>
       </c>
@@ -2014,13 +2045,13 @@
       <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="8" t="s">
         <v>89</v>
       </c>
     </row>
@@ -2031,13 +2062,13 @@
       <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="8" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2048,13 +2079,13 @@
       <c r="B4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="8" t="s">
         <v>95</v>
       </c>
     </row>
@@ -2065,13 +2096,13 @@
       <c r="B5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="8" t="s">
         <v>97</v>
       </c>
     </row>
@@ -2082,13 +2113,13 @@
       <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="8" t="s">
         <v>97</v>
       </c>
     </row>
@@ -2099,13 +2130,13 @@
       <c r="B7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="8" t="s">
         <v>100</v>
       </c>
     </row>
@@ -2116,13 +2147,13 @@
       <c r="B8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="8" t="s">
         <v>290</v>
       </c>
     </row>
@@ -2133,9 +2164,15 @@
       <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
+      <c r="C9" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>299</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="15">
       <c r="A10" s="2">
@@ -2144,13 +2181,13 @@
       <c r="B10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="8" t="s">
         <v>103</v>
       </c>
     </row>
@@ -2161,11 +2198,13 @@
       <c r="B11" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2" t="s">
+      <c r="D11" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2176,13 +2215,13 @@
       <c r="B12" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="8" t="s">
         <v>108</v>
       </c>
     </row>
@@ -2193,9 +2232,15 @@
       <c r="B13" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
+      <c r="C13" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="14" spans="1:5" ht="15">
       <c r="A14" s="2">
@@ -2204,13 +2249,13 @@
       <c r="B14" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="8" t="s">
         <v>292</v>
       </c>
     </row>
@@ -2221,13 +2266,13 @@
       <c r="B15" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="8" t="s">
         <v>288</v>
       </c>
     </row>
@@ -2238,9 +2283,15 @@
       <c r="B16" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
+      <c r="C16" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="17" spans="1:7" ht="15">
       <c r="A17" s="2">
@@ -2249,13 +2300,13 @@
       <c r="B17" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="8" t="s">
         <v>294</v>
       </c>
     </row>
@@ -4488,17 +4539,18 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="2" width="40" customWidth="1"/>
+    <col min="1" max="1" width="82.33203125" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
     </row>
     <row r="3" spans="1:5" ht="16">
       <c r="A3" s="4" t="s">
@@ -4524,19 +4576,19 @@
       </c>
       <c r="B6" s="2"/>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5" ht="15">
       <c r="A7" s="2" t="s">
         <v>282</v>
       </c>
       <c r="B7" s="2"/>
     </row>
-    <row r="8" spans="1:5" ht="30">
+    <row r="8" spans="1:5" ht="15">
       <c r="A8" s="2" t="s">
         <v>283</v>
       </c>
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="15">
       <c r="A9" s="2" t="s">
         <v>284</v>
       </c>
